--- a/V9_W8_B32/data_instructions/VLIW_Excel/Unit5_1_DownSamplingL.xlsx
+++ b/V9_W8_B32/data_instructions/VLIW_Excel/Unit5_1_DownSamplingL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V7\data_instructions\VLIW_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V9_W8_B32\data_instructions\VLIW_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA577E70-8321-47C1-8628-FCDFA310B7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186387A3-0AC8-4282-AC67-5740690169CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{8075A957-5B64-468D-B2D4-F19799456396}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{8075A957-5B64-468D-B2D4-F19799456396}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="103">
   <si>
     <t>OP_Code</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -446,6 +446,10 @@
   </si>
   <si>
     <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Requant_Sel[3]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -686,10 +690,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -701,7 +702,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1167,6 +1171,9 @@
       <c r="M5" s="8" t="s">
         <v>92</v>
       </c>
+      <c r="N5" s="7" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
@@ -1177,7 +1184,7 @@
       </c>
       <c r="D7" s="23"/>
       <c r="E7" s="23"/>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="29" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="23"/>
@@ -1212,7 +1219,7 @@
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
-      <c r="F8" s="24"/>
+      <c r="F8" s="29"/>
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
       <c r="I8" s="23"/>
@@ -1255,7 +1262,7 @@
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
-      <c r="F9" s="24"/>
+      <c r="F9" s="29"/>
       <c r="G9" s="23"/>
       <c r="H9" s="23"/>
       <c r="I9" s="23"/>
@@ -1279,7 +1286,7 @@
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="23"/>
-      <c r="F10" s="24"/>
+      <c r="F10" s="29"/>
       <c r="G10" s="23"/>
       <c r="H10" s="23"/>
       <c r="I10" s="23"/>
@@ -1310,7 +1317,7 @@
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
       <c r="E11" s="23"/>
-      <c r="F11" s="24"/>
+      <c r="F11" s="29"/>
       <c r="G11" s="23"/>
       <c r="H11" s="23"/>
       <c r="I11" s="23"/>
@@ -1344,7 +1351,7 @@
       <c r="F12" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="29" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="23"/>
@@ -1379,7 +1386,7 @@
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
-      <c r="G13" s="24"/>
+      <c r="G13" s="29"/>
       <c r="H13" s="23"/>
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
@@ -1422,7 +1429,7 @@
       <c r="D14" s="23"/>
       <c r="E14" s="23"/>
       <c r="F14" s="23"/>
-      <c r="G14" s="24"/>
+      <c r="G14" s="29"/>
       <c r="H14" s="23"/>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
@@ -1446,7 +1453,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
-      <c r="G15" s="24"/>
+      <c r="G15" s="29"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -1477,7 +1484,7 @@
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
-      <c r="G16" s="24"/>
+      <c r="G16" s="29"/>
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
@@ -1504,14 +1511,14 @@
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="23"/>
-      <c r="F17" s="28" t="s">
+      <c r="F17" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="28" t="s">
+      <c r="G17" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H17" s="23"/>
-      <c r="I17" s="25" t="s">
+      <c r="I17" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J17" s="23"/>
@@ -1543,10 +1550,10 @@
       <c r="C18" s="23"/>
       <c r="D18" s="23"/>
       <c r="E18" s="23"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
       <c r="H18" s="23"/>
-      <c r="I18" s="25"/>
+      <c r="I18" s="28"/>
       <c r="J18" s="23"/>
       <c r="L18" s="11" t="s">
         <v>5</v>
@@ -1586,10 +1593,10 @@
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
       <c r="H19" s="23"/>
-      <c r="I19" s="25"/>
+      <c r="I19" s="28"/>
       <c r="J19" s="23"/>
       <c r="L19" s="12" t="s">
         <v>15</v>
@@ -1619,10 +1626,10 @@
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
       <c r="E20" s="23"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
       <c r="H20" s="23"/>
-      <c r="I20" s="25"/>
+      <c r="I20" s="28"/>
       <c r="J20" s="23"/>
       <c r="L20" s="14" t="s">
         <v>17</v>
@@ -1649,10 +1656,10 @@
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
       <c r="E21" s="23"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
       <c r="H21" s="23"/>
-      <c r="I21" s="25"/>
+      <c r="I21" s="28"/>
       <c r="J21" s="23"/>
       <c r="L21" s="15" t="s">
         <v>23</v>
@@ -1699,10 +1706,10 @@
       <c r="G24" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I24" s="26" t="s">
+      <c r="H24" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="25" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="23"/>
@@ -1736,8 +1743,8 @@
       <c r="E25" s="23"/>
       <c r="F25" s="23"/>
       <c r="G25" s="23"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="27"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="26"/>
       <c r="J25" s="23"/>
       <c r="L25" s="11" t="s">
         <v>5</v>
@@ -1779,8 +1786,8 @@
       <c r="E26" s="23"/>
       <c r="F26" s="23"/>
       <c r="G26" s="23"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="27"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="26"/>
       <c r="J26" s="23"/>
       <c r="L26" s="12" t="s">
         <v>15</v>
@@ -1804,8 +1811,8 @@
       <c r="E27" s="23"/>
       <c r="F27" s="23"/>
       <c r="G27" s="23"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="27"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="26"/>
       <c r="J27" s="23"/>
       <c r="L27" s="14" t="s">
         <v>17</v>
@@ -1835,8 +1842,8 @@
       <c r="E28" s="23"/>
       <c r="F28" s="23"/>
       <c r="G28" s="23"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="27"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="26"/>
       <c r="J28" s="23"/>
       <c r="L28" s="15" t="s">
         <v>23</v>
@@ -1864,7 +1871,7 @@
       </c>
       <c r="D29" s="23"/>
       <c r="E29" s="23"/>
-      <c r="F29" s="24" t="s">
+      <c r="F29" s="29" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="23" t="s">
@@ -1873,10 +1880,10 @@
       <c r="H29" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I29" s="28" t="s">
+      <c r="I29" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J29" s="25" t="s">
+      <c r="J29" s="28" t="s">
         <v>26</v>
       </c>
       <c r="L29" s="9" t="s">
@@ -1907,11 +1914,11 @@
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
       <c r="E30" s="23"/>
-      <c r="F30" s="24"/>
+      <c r="F30" s="29"/>
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="25"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="28"/>
       <c r="L30" s="11" t="s">
         <v>5</v>
       </c>
@@ -1953,11 +1960,11 @@
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="24"/>
+      <c r="F31" s="29"/>
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="25"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="28"/>
       <c r="L31" s="12" t="s">
         <v>15</v>
       </c>
@@ -1986,11 +1993,11 @@
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
       <c r="E32" s="23"/>
-      <c r="F32" s="24"/>
+      <c r="F32" s="29"/>
       <c r="G32" s="23"/>
       <c r="H32" s="23"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="25"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="28"/>
       <c r="L32" s="14" t="s">
         <v>17</v>
       </c>
@@ -2017,11 +2024,11 @@
       <c r="C33" s="23"/>
       <c r="D33" s="23"/>
       <c r="E33" s="23"/>
-      <c r="F33" s="24"/>
+      <c r="F33" s="29"/>
       <c r="G33" s="23"/>
       <c r="H33" s="23"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="25"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="28"/>
       <c r="L33" s="15" t="s">
         <v>23</v>
       </c>
@@ -2048,19 +2055,19 @@
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="23"/>
-      <c r="F34" s="28" t="s">
+      <c r="F34" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G34" s="28" t="s">
+      <c r="G34" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="28" t="s">
+      <c r="H34" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I34" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" s="29" t="s">
+      <c r="I34" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" s="24" t="s">
         <v>34</v>
       </c>
       <c r="L34" s="9" t="s">
@@ -2091,11 +2098,11 @@
       <c r="C35" s="23"/>
       <c r="D35" s="23"/>
       <c r="E35" s="23"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="29"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="24"/>
       <c r="L35" s="11" t="s">
         <v>5</v>
       </c>
@@ -2134,11 +2141,11 @@
       <c r="C36" s="23"/>
       <c r="D36" s="23"/>
       <c r="E36" s="23"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="29"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="24"/>
       <c r="L36" s="12" t="s">
         <v>15</v>
       </c>
@@ -2167,11 +2174,11 @@
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
       <c r="E37" s="23"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="29"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="24"/>
       <c r="L37" s="14" t="s">
         <v>17</v>
       </c>
@@ -2198,11 +2205,11 @@
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
       <c r="E38" s="23"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="29"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="24"/>
       <c r="L38" s="15" t="s">
         <v>23</v>
       </c>
@@ -2235,11 +2242,11 @@
       <c r="F40" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G40" s="24" t="s">
+      <c r="G40" s="29" t="s">
         <v>26</v>
       </c>
       <c r="H40" s="23"/>
-      <c r="I40" s="26" t="s">
+      <c r="I40" s="25" t="s">
         <v>41</v>
       </c>
       <c r="J40" s="23"/>
@@ -2272,9 +2279,9 @@
       <c r="D41" s="23"/>
       <c r="E41" s="23"/>
       <c r="F41" s="23"/>
-      <c r="G41" s="24"/>
+      <c r="G41" s="29"/>
       <c r="H41" s="23"/>
-      <c r="I41" s="27"/>
+      <c r="I41" s="26"/>
       <c r="J41" s="23"/>
       <c r="L41" s="11" t="s">
         <v>5</v>
@@ -2315,9 +2322,9 @@
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
       <c r="F42" s="23"/>
-      <c r="G42" s="24"/>
+      <c r="G42" s="29"/>
       <c r="H42" s="23"/>
-      <c r="I42" s="27"/>
+      <c r="I42" s="26"/>
       <c r="J42" s="23"/>
       <c r="L42" s="12" t="s">
         <v>15</v>
@@ -2340,9 +2347,9 @@
       <c r="D43" s="23"/>
       <c r="E43" s="23"/>
       <c r="F43" s="23"/>
-      <c r="G43" s="24"/>
+      <c r="G43" s="29"/>
       <c r="H43" s="23"/>
-      <c r="I43" s="27"/>
+      <c r="I43" s="26"/>
       <c r="J43" s="23"/>
       <c r="L43" s="14" t="s">
         <v>17</v>
@@ -2371,9 +2378,9 @@
       <c r="D44" s="23"/>
       <c r="E44" s="23"/>
       <c r="F44" s="23"/>
-      <c r="G44" s="24"/>
+      <c r="G44" s="29"/>
       <c r="H44" s="23"/>
-      <c r="I44" s="27"/>
+      <c r="I44" s="26"/>
       <c r="J44" s="23"/>
       <c r="L44" s="15" t="s">
         <v>23</v>
@@ -2407,13 +2414,13 @@
       <c r="G45" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H45" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I45" s="28" t="s">
+      <c r="H45" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J45" s="25" t="s">
+      <c r="J45" s="28" t="s">
         <v>26</v>
       </c>
       <c r="L45" s="9" t="s">
@@ -2446,9 +2453,9 @@
       <c r="E46" s="23"/>
       <c r="F46" s="23"/>
       <c r="G46" s="23"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="25"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="27"/>
+      <c r="J46" s="28"/>
       <c r="L46" s="11" t="s">
         <v>5</v>
       </c>
@@ -2489,9 +2496,9 @@
       <c r="E47" s="23"/>
       <c r="F47" s="23"/>
       <c r="G47" s="23"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="25"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="28"/>
       <c r="L47" s="12" t="s">
         <v>15</v>
       </c>
@@ -2522,9 +2529,9 @@
       <c r="E48" s="23"/>
       <c r="F48" s="23"/>
       <c r="G48" s="23"/>
-      <c r="H48" s="24"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="25"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="28"/>
       <c r="L48" s="14" t="s">
         <v>17</v>
       </c>
@@ -2553,9 +2560,9 @@
       <c r="E49" s="23"/>
       <c r="F49" s="23"/>
       <c r="G49" s="23"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="25"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="28"/>
       <c r="L49" s="15" t="s">
         <v>23</v>
       </c>
@@ -2582,19 +2589,19 @@
       </c>
       <c r="D50" s="23"/>
       <c r="E50" s="23"/>
-      <c r="F50" s="28" t="s">
+      <c r="F50" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G50" s="28" t="s">
+      <c r="G50" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H50" s="28" t="s">
+      <c r="H50" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I50" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J50" s="29" t="s">
+      <c r="I50" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J50" s="24" t="s">
         <v>34</v>
       </c>
       <c r="L50" s="9" t="s">
@@ -2625,11 +2632,11 @@
       <c r="C51" s="23"/>
       <c r="D51" s="23"/>
       <c r="E51" s="23"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="25"/>
-      <c r="J51" s="29"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="27"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="24"/>
       <c r="L51" s="11" t="s">
         <v>5</v>
       </c>
@@ -2668,11 +2675,11 @@
       <c r="C52" s="23"/>
       <c r="D52" s="23"/>
       <c r="E52" s="23"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="25"/>
-      <c r="J52" s="29"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="24"/>
       <c r="L52" s="12" t="s">
         <v>15</v>
       </c>
@@ -2701,11 +2708,11 @@
       <c r="C53" s="23"/>
       <c r="D53" s="23"/>
       <c r="E53" s="23"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="25"/>
-      <c r="J53" s="29"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="24"/>
       <c r="L53" s="14" t="s">
         <v>17</v>
       </c>
@@ -2732,11 +2739,11 @@
       <c r="C54" s="23"/>
       <c r="D54" s="23"/>
       <c r="E54" s="23"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="25"/>
-      <c r="J54" s="29"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="24"/>
       <c r="L54" s="15" t="s">
         <v>23</v>
       </c>
@@ -2766,14 +2773,14 @@
       </c>
       <c r="D56" s="23"/>
       <c r="E56" s="23"/>
-      <c r="F56" s="24" t="s">
+      <c r="F56" s="29" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="23"/>
       <c r="H56" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I56" s="26" t="s">
+      <c r="I56" s="25" t="s">
         <v>41</v>
       </c>
       <c r="J56" s="23"/>
@@ -2805,10 +2812,10 @@
       <c r="C57" s="23"/>
       <c r="D57" s="23"/>
       <c r="E57" s="23"/>
-      <c r="F57" s="24"/>
+      <c r="F57" s="29"/>
       <c r="G57" s="23"/>
       <c r="H57" s="23"/>
-      <c r="I57" s="27"/>
+      <c r="I57" s="26"/>
       <c r="J57" s="23"/>
       <c r="L57" s="11" t="s">
         <v>5</v>
@@ -2848,10 +2855,10 @@
       <c r="C58" s="23"/>
       <c r="D58" s="23"/>
       <c r="E58" s="23"/>
-      <c r="F58" s="24"/>
+      <c r="F58" s="29"/>
       <c r="G58" s="23"/>
       <c r="H58" s="23"/>
-      <c r="I58" s="27"/>
+      <c r="I58" s="26"/>
       <c r="J58" s="23"/>
       <c r="L58" s="12" t="s">
         <v>15</v>
@@ -2873,10 +2880,10 @@
       <c r="C59" s="23"/>
       <c r="D59" s="23"/>
       <c r="E59" s="23"/>
-      <c r="F59" s="24"/>
+      <c r="F59" s="29"/>
       <c r="G59" s="23"/>
       <c r="H59" s="23"/>
-      <c r="I59" s="27"/>
+      <c r="I59" s="26"/>
       <c r="J59" s="23"/>
       <c r="L59" s="14" t="s">
         <v>17</v>
@@ -2904,10 +2911,10 @@
       <c r="C60" s="23"/>
       <c r="D60" s="23"/>
       <c r="E60" s="23"/>
-      <c r="F60" s="24"/>
+      <c r="F60" s="29"/>
       <c r="G60" s="23"/>
       <c r="H60" s="23"/>
-      <c r="I60" s="27"/>
+      <c r="I60" s="26"/>
       <c r="J60" s="23"/>
       <c r="L60" s="15" t="s">
         <v>23</v>
@@ -2938,16 +2945,16 @@
       <c r="F61" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="24" t="s">
+      <c r="G61" s="29" t="s">
         <v>26</v>
       </c>
       <c r="H61" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I61" s="28" t="s">
+      <c r="I61" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J61" s="25" t="s">
+      <c r="J61" s="28" t="s">
         <v>26</v>
       </c>
       <c r="L61" s="9" t="s">
@@ -2979,10 +2986,10 @@
       <c r="D62" s="23"/>
       <c r="E62" s="23"/>
       <c r="F62" s="23"/>
-      <c r="G62" s="24"/>
+      <c r="G62" s="29"/>
       <c r="H62" s="23"/>
-      <c r="I62" s="28"/>
-      <c r="J62" s="25"/>
+      <c r="I62" s="27"/>
+      <c r="J62" s="28"/>
       <c r="L62" s="11" t="s">
         <v>5</v>
       </c>
@@ -3022,10 +3029,10 @@
       <c r="D63" s="23"/>
       <c r="E63" s="23"/>
       <c r="F63" s="23"/>
-      <c r="G63" s="24"/>
+      <c r="G63" s="29"/>
       <c r="H63" s="23"/>
-      <c r="I63" s="28"/>
-      <c r="J63" s="25"/>
+      <c r="I63" s="27"/>
+      <c r="J63" s="28"/>
       <c r="L63" s="12" t="s">
         <v>15</v>
       </c>
@@ -3055,10 +3062,10 @@
       <c r="D64" s="23"/>
       <c r="E64" s="23"/>
       <c r="F64" s="23"/>
-      <c r="G64" s="24"/>
+      <c r="G64" s="29"/>
       <c r="H64" s="23"/>
-      <c r="I64" s="28"/>
-      <c r="J64" s="25"/>
+      <c r="I64" s="27"/>
+      <c r="J64" s="28"/>
       <c r="L64" s="14" t="s">
         <v>17</v>
       </c>
@@ -3086,10 +3093,10 @@
       <c r="D65" s="23"/>
       <c r="E65" s="23"/>
       <c r="F65" s="23"/>
-      <c r="G65" s="24"/>
+      <c r="G65" s="29"/>
       <c r="H65" s="23"/>
-      <c r="I65" s="28"/>
-      <c r="J65" s="25"/>
+      <c r="I65" s="27"/>
+      <c r="J65" s="28"/>
       <c r="L65" s="15" t="s">
         <v>23</v>
       </c>
@@ -3116,19 +3123,19 @@
       </c>
       <c r="D66" s="23"/>
       <c r="E66" s="23"/>
-      <c r="F66" s="28" t="s">
+      <c r="F66" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G66" s="28" t="s">
+      <c r="G66" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H66" s="28" t="s">
+      <c r="H66" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I66" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J66" s="29" t="s">
+      <c r="I66" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J66" s="24" t="s">
         <v>34</v>
       </c>
       <c r="L66" s="9" t="s">
@@ -3159,11 +3166,11 @@
       <c r="C67" s="23"/>
       <c r="D67" s="23"/>
       <c r="E67" s="23"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="25"/>
-      <c r="J67" s="29"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="28"/>
+      <c r="J67" s="24"/>
       <c r="L67" s="11" t="s">
         <v>5</v>
       </c>
@@ -3202,11 +3209,11 @@
       <c r="C68" s="23"/>
       <c r="D68" s="23"/>
       <c r="E68" s="23"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="25"/>
-      <c r="J68" s="29"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="27"/>
+      <c r="I68" s="28"/>
+      <c r="J68" s="24"/>
       <c r="L68" s="12" t="s">
         <v>15</v>
       </c>
@@ -3235,11 +3242,11 @@
       <c r="C69" s="23"/>
       <c r="D69" s="23"/>
       <c r="E69" s="23"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="25"/>
-      <c r="J69" s="29"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="27"/>
+      <c r="H69" s="27"/>
+      <c r="I69" s="28"/>
+      <c r="J69" s="24"/>
       <c r="L69" s="14" t="s">
         <v>17</v>
       </c>
@@ -3266,11 +3273,11 @@
       <c r="C70" s="23"/>
       <c r="D70" s="23"/>
       <c r="E70" s="23"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="25"/>
-      <c r="J70" s="29"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="28"/>
+      <c r="J70" s="24"/>
       <c r="L70" s="15" t="s">
         <v>23</v>
       </c>
@@ -3325,10 +3332,10 @@
       <c r="G73" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H73" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I73" s="26" t="s">
+      <c r="H73" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I73" s="25" t="s">
         <v>41</v>
       </c>
       <c r="J73" s="23"/>
@@ -3362,8 +3369,8 @@
       <c r="E74" s="23"/>
       <c r="F74" s="23"/>
       <c r="G74" s="23"/>
-      <c r="H74" s="24"/>
-      <c r="I74" s="27"/>
+      <c r="H74" s="29"/>
+      <c r="I74" s="26"/>
       <c r="J74" s="23"/>
       <c r="L74" s="11" t="s">
         <v>5</v>
@@ -3405,8 +3412,8 @@
       <c r="E75" s="23"/>
       <c r="F75" s="23"/>
       <c r="G75" s="23"/>
-      <c r="H75" s="24"/>
-      <c r="I75" s="27"/>
+      <c r="H75" s="29"/>
+      <c r="I75" s="26"/>
       <c r="J75" s="23"/>
       <c r="L75" s="12" t="s">
         <v>15</v>
@@ -3430,8 +3437,8 @@
       <c r="E76" s="23"/>
       <c r="F76" s="23"/>
       <c r="G76" s="23"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="27"/>
+      <c r="H76" s="29"/>
+      <c r="I76" s="26"/>
       <c r="J76" s="23"/>
       <c r="L76" s="14" t="s">
         <v>17</v>
@@ -3461,8 +3468,8 @@
       <c r="E77" s="23"/>
       <c r="F77" s="23"/>
       <c r="G77" s="23"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="27"/>
+      <c r="H77" s="29"/>
+      <c r="I77" s="26"/>
       <c r="J77" s="23"/>
       <c r="L77" s="15" t="s">
         <v>23</v>
@@ -3490,7 +3497,7 @@
       </c>
       <c r="D78" s="23"/>
       <c r="E78" s="23"/>
-      <c r="F78" s="24" t="s">
+      <c r="F78" s="29" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="23" t="s">
@@ -3499,10 +3506,10 @@
       <c r="H78" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I78" s="28" t="s">
+      <c r="I78" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J78" s="25" t="s">
+      <c r="J78" s="28" t="s">
         <v>26</v>
       </c>
       <c r="L78" s="9" t="s">
@@ -3533,11 +3540,11 @@
       <c r="C79" s="23"/>
       <c r="D79" s="23"/>
       <c r="E79" s="23"/>
-      <c r="F79" s="24"/>
+      <c r="F79" s="29"/>
       <c r="G79" s="23"/>
       <c r="H79" s="23"/>
-      <c r="I79" s="28"/>
-      <c r="J79" s="25"/>
+      <c r="I79" s="27"/>
+      <c r="J79" s="28"/>
       <c r="L79" s="11" t="s">
         <v>5</v>
       </c>
@@ -3576,11 +3583,11 @@
       <c r="C80" s="23"/>
       <c r="D80" s="23"/>
       <c r="E80" s="23"/>
-      <c r="F80" s="24"/>
+      <c r="F80" s="29"/>
       <c r="G80" s="23"/>
       <c r="H80" s="23"/>
-      <c r="I80" s="28"/>
-      <c r="J80" s="25"/>
+      <c r="I80" s="27"/>
+      <c r="J80" s="28"/>
       <c r="L80" s="12" t="s">
         <v>15</v>
       </c>
@@ -3609,11 +3616,11 @@
       <c r="C81" s="23"/>
       <c r="D81" s="23"/>
       <c r="E81" s="23"/>
-      <c r="F81" s="24"/>
+      <c r="F81" s="29"/>
       <c r="G81" s="23"/>
       <c r="H81" s="23"/>
-      <c r="I81" s="28"/>
-      <c r="J81" s="25"/>
+      <c r="I81" s="27"/>
+      <c r="J81" s="28"/>
       <c r="L81" s="14" t="s">
         <v>17</v>
       </c>
@@ -3640,11 +3647,11 @@
       <c r="C82" s="23"/>
       <c r="D82" s="23"/>
       <c r="E82" s="23"/>
-      <c r="F82" s="24"/>
+      <c r="F82" s="29"/>
       <c r="G82" s="23"/>
       <c r="H82" s="23"/>
-      <c r="I82" s="28"/>
-      <c r="J82" s="25"/>
+      <c r="I82" s="27"/>
+      <c r="J82" s="28"/>
       <c r="L82" s="15" t="s">
         <v>23</v>
       </c>
@@ -3671,19 +3678,19 @@
       </c>
       <c r="D83" s="23"/>
       <c r="E83" s="23"/>
-      <c r="F83" s="28" t="s">
+      <c r="F83" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G83" s="28" t="s">
+      <c r="G83" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H83" s="28" t="s">
+      <c r="H83" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I83" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J83" s="29" t="s">
+      <c r="I83" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J83" s="24" t="s">
         <v>34</v>
       </c>
       <c r="L83" s="9" t="s">
@@ -3714,11 +3721,11 @@
       <c r="C84" s="23"/>
       <c r="D84" s="23"/>
       <c r="E84" s="23"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="28"/>
-      <c r="I84" s="25"/>
-      <c r="J84" s="29"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="27"/>
+      <c r="H84" s="27"/>
+      <c r="I84" s="28"/>
+      <c r="J84" s="24"/>
       <c r="L84" s="11" t="s">
         <v>5</v>
       </c>
@@ -3757,11 +3764,11 @@
       <c r="C85" s="23"/>
       <c r="D85" s="23"/>
       <c r="E85" s="23"/>
-      <c r="F85" s="28"/>
-      <c r="G85" s="28"/>
-      <c r="H85" s="28"/>
-      <c r="I85" s="25"/>
-      <c r="J85" s="29"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="27"/>
+      <c r="H85" s="27"/>
+      <c r="I85" s="28"/>
+      <c r="J85" s="24"/>
       <c r="L85" s="12" t="s">
         <v>15</v>
       </c>
@@ -3790,11 +3797,11 @@
       <c r="C86" s="23"/>
       <c r="D86" s="23"/>
       <c r="E86" s="23"/>
-      <c r="F86" s="28"/>
-      <c r="G86" s="28"/>
-      <c r="H86" s="28"/>
-      <c r="I86" s="25"/>
-      <c r="J86" s="29"/>
+      <c r="F86" s="27"/>
+      <c r="G86" s="27"/>
+      <c r="H86" s="27"/>
+      <c r="I86" s="28"/>
+      <c r="J86" s="24"/>
       <c r="L86" s="14" t="s">
         <v>17</v>
       </c>
@@ -3821,11 +3828,11 @@
       <c r="C87" s="23"/>
       <c r="D87" s="23"/>
       <c r="E87" s="23"/>
-      <c r="F87" s="28"/>
-      <c r="G87" s="28"/>
-      <c r="H87" s="28"/>
-      <c r="I87" s="25"/>
-      <c r="J87" s="29"/>
+      <c r="F87" s="27"/>
+      <c r="G87" s="27"/>
+      <c r="H87" s="27"/>
+      <c r="I87" s="28"/>
+      <c r="J87" s="24"/>
       <c r="L87" s="15" t="s">
         <v>23</v>
       </c>
@@ -3858,11 +3865,11 @@
       <c r="F89" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G89" s="24" t="s">
+      <c r="G89" s="29" t="s">
         <v>26</v>
       </c>
       <c r="H89" s="23"/>
-      <c r="I89" s="26" t="s">
+      <c r="I89" s="25" t="s">
         <v>41</v>
       </c>
       <c r="J89" s="23"/>
@@ -3895,9 +3902,9 @@
       <c r="D90" s="23"/>
       <c r="E90" s="23"/>
       <c r="F90" s="23"/>
-      <c r="G90" s="24"/>
+      <c r="G90" s="29"/>
       <c r="H90" s="23"/>
-      <c r="I90" s="27"/>
+      <c r="I90" s="26"/>
       <c r="J90" s="23"/>
       <c r="L90" s="11" t="s">
         <v>5</v>
@@ -3938,9 +3945,9 @@
       <c r="D91" s="23"/>
       <c r="E91" s="23"/>
       <c r="F91" s="23"/>
-      <c r="G91" s="24"/>
+      <c r="G91" s="29"/>
       <c r="H91" s="23"/>
-      <c r="I91" s="27"/>
+      <c r="I91" s="26"/>
       <c r="J91" s="23"/>
       <c r="L91" s="12" t="s">
         <v>15</v>
@@ -3963,9 +3970,9 @@
       <c r="D92" s="23"/>
       <c r="E92" s="23"/>
       <c r="F92" s="23"/>
-      <c r="G92" s="24"/>
+      <c r="G92" s="29"/>
       <c r="H92" s="23"/>
-      <c r="I92" s="27"/>
+      <c r="I92" s="26"/>
       <c r="J92" s="23"/>
       <c r="L92" s="14" t="s">
         <v>17</v>
@@ -3994,9 +4001,9 @@
       <c r="D93" s="23"/>
       <c r="E93" s="23"/>
       <c r="F93" s="23"/>
-      <c r="G93" s="24"/>
+      <c r="G93" s="29"/>
       <c r="H93" s="23"/>
-      <c r="I93" s="27"/>
+      <c r="I93" s="26"/>
       <c r="J93" s="23"/>
       <c r="L93" s="15" t="s">
         <v>23</v>
@@ -4030,13 +4037,13 @@
       <c r="G94" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H94" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I94" s="28" t="s">
+      <c r="H94" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I94" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J94" s="25" t="s">
+      <c r="J94" s="28" t="s">
         <v>26</v>
       </c>
       <c r="L94" s="9" t="s">
@@ -4069,9 +4076,9 @@
       <c r="E95" s="23"/>
       <c r="F95" s="23"/>
       <c r="G95" s="23"/>
-      <c r="H95" s="24"/>
-      <c r="I95" s="28"/>
-      <c r="J95" s="25"/>
+      <c r="H95" s="29"/>
+      <c r="I95" s="27"/>
+      <c r="J95" s="28"/>
       <c r="L95" s="11" t="s">
         <v>5</v>
       </c>
@@ -4112,9 +4119,9 @@
       <c r="E96" s="23"/>
       <c r="F96" s="23"/>
       <c r="G96" s="23"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="28"/>
-      <c r="J96" s="25"/>
+      <c r="H96" s="29"/>
+      <c r="I96" s="27"/>
+      <c r="J96" s="28"/>
       <c r="L96" s="12" t="s">
         <v>15</v>
       </c>
@@ -4145,9 +4152,9 @@
       <c r="E97" s="23"/>
       <c r="F97" s="23"/>
       <c r="G97" s="23"/>
-      <c r="H97" s="24"/>
-      <c r="I97" s="28"/>
-      <c r="J97" s="25"/>
+      <c r="H97" s="29"/>
+      <c r="I97" s="27"/>
+      <c r="J97" s="28"/>
       <c r="L97" s="14" t="s">
         <v>17</v>
       </c>
@@ -4176,9 +4183,9 @@
       <c r="E98" s="23"/>
       <c r="F98" s="23"/>
       <c r="G98" s="23"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="28"/>
-      <c r="J98" s="25"/>
+      <c r="H98" s="29"/>
+      <c r="I98" s="27"/>
+      <c r="J98" s="28"/>
       <c r="L98" s="15" t="s">
         <v>23</v>
       </c>
@@ -4205,19 +4212,19 @@
       </c>
       <c r="D99" s="23"/>
       <c r="E99" s="23"/>
-      <c r="F99" s="28" t="s">
+      <c r="F99" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G99" s="28" t="s">
+      <c r="G99" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H99" s="28" t="s">
+      <c r="H99" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I99" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J99" s="29" t="s">
+      <c r="I99" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J99" s="24" t="s">
         <v>34</v>
       </c>
       <c r="L99" s="9" t="s">
@@ -4248,11 +4255,11 @@
       <c r="C100" s="23"/>
       <c r="D100" s="23"/>
       <c r="E100" s="23"/>
-      <c r="F100" s="28"/>
-      <c r="G100" s="28"/>
-      <c r="H100" s="28"/>
-      <c r="I100" s="25"/>
-      <c r="J100" s="29"/>
+      <c r="F100" s="27"/>
+      <c r="G100" s="27"/>
+      <c r="H100" s="27"/>
+      <c r="I100" s="28"/>
+      <c r="J100" s="24"/>
       <c r="L100" s="11" t="s">
         <v>5</v>
       </c>
@@ -4291,11 +4298,11 @@
       <c r="C101" s="23"/>
       <c r="D101" s="23"/>
       <c r="E101" s="23"/>
-      <c r="F101" s="28"/>
-      <c r="G101" s="28"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="25"/>
-      <c r="J101" s="29"/>
+      <c r="F101" s="27"/>
+      <c r="G101" s="27"/>
+      <c r="H101" s="27"/>
+      <c r="I101" s="28"/>
+      <c r="J101" s="24"/>
       <c r="L101" s="12" t="s">
         <v>15</v>
       </c>
@@ -4324,11 +4331,11 @@
       <c r="C102" s="23"/>
       <c r="D102" s="23"/>
       <c r="E102" s="23"/>
-      <c r="F102" s="28"/>
-      <c r="G102" s="28"/>
-      <c r="H102" s="28"/>
-      <c r="I102" s="25"/>
-      <c r="J102" s="29"/>
+      <c r="F102" s="27"/>
+      <c r="G102" s="27"/>
+      <c r="H102" s="27"/>
+      <c r="I102" s="28"/>
+      <c r="J102" s="24"/>
       <c r="L102" s="14" t="s">
         <v>17</v>
       </c>
@@ -4355,11 +4362,11 @@
       <c r="C103" s="23"/>
       <c r="D103" s="23"/>
       <c r="E103" s="23"/>
-      <c r="F103" s="28"/>
-      <c r="G103" s="28"/>
-      <c r="H103" s="28"/>
-      <c r="I103" s="25"/>
-      <c r="J103" s="29"/>
+      <c r="F103" s="27"/>
+      <c r="G103" s="27"/>
+      <c r="H103" s="27"/>
+      <c r="I103" s="28"/>
+      <c r="J103" s="24"/>
       <c r="L103" s="15" t="s">
         <v>23</v>
       </c>
@@ -4389,14 +4396,14 @@
       </c>
       <c r="D105" s="23"/>
       <c r="E105" s="23"/>
-      <c r="F105" s="24" t="s">
+      <c r="F105" s="29" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="23"/>
       <c r="H105" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I105" s="26" t="s">
+      <c r="I105" s="25" t="s">
         <v>41</v>
       </c>
       <c r="J105" s="23"/>
@@ -4428,10 +4435,10 @@
       <c r="C106" s="23"/>
       <c r="D106" s="23"/>
       <c r="E106" s="23"/>
-      <c r="F106" s="24"/>
+      <c r="F106" s="29"/>
       <c r="G106" s="23"/>
       <c r="H106" s="23"/>
-      <c r="I106" s="27"/>
+      <c r="I106" s="26"/>
       <c r="J106" s="23"/>
       <c r="L106" s="11" t="s">
         <v>5</v>
@@ -4471,10 +4478,10 @@
       <c r="C107" s="23"/>
       <c r="D107" s="23"/>
       <c r="E107" s="23"/>
-      <c r="F107" s="24"/>
+      <c r="F107" s="29"/>
       <c r="G107" s="23"/>
       <c r="H107" s="23"/>
-      <c r="I107" s="27"/>
+      <c r="I107" s="26"/>
       <c r="J107" s="23"/>
       <c r="L107" s="12" t="s">
         <v>15</v>
@@ -4496,10 +4503,10 @@
       <c r="C108" s="23"/>
       <c r="D108" s="23"/>
       <c r="E108" s="23"/>
-      <c r="F108" s="24"/>
+      <c r="F108" s="29"/>
       <c r="G108" s="23"/>
       <c r="H108" s="23"/>
-      <c r="I108" s="27"/>
+      <c r="I108" s="26"/>
       <c r="J108" s="23"/>
       <c r="L108" s="14" t="s">
         <v>17</v>
@@ -4527,10 +4534,10 @@
       <c r="C109" s="23"/>
       <c r="D109" s="23"/>
       <c r="E109" s="23"/>
-      <c r="F109" s="24"/>
+      <c r="F109" s="29"/>
       <c r="G109" s="23"/>
       <c r="H109" s="23"/>
-      <c r="I109" s="27"/>
+      <c r="I109" s="26"/>
       <c r="J109" s="23"/>
       <c r="L109" s="15" t="s">
         <v>23</v>
@@ -4561,16 +4568,16 @@
       <c r="F110" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G110" s="24" t="s">
+      <c r="G110" s="29" t="s">
         <v>26</v>
       </c>
       <c r="H110" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I110" s="28" t="s">
+      <c r="I110" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J110" s="25" t="s">
+      <c r="J110" s="28" t="s">
         <v>26</v>
       </c>
       <c r="L110" s="9" t="s">
@@ -4602,10 +4609,10 @@
       <c r="D111" s="23"/>
       <c r="E111" s="23"/>
       <c r="F111" s="23"/>
-      <c r="G111" s="24"/>
+      <c r="G111" s="29"/>
       <c r="H111" s="23"/>
-      <c r="I111" s="28"/>
-      <c r="J111" s="25"/>
+      <c r="I111" s="27"/>
+      <c r="J111" s="28"/>
       <c r="L111" s="11" t="s">
         <v>5</v>
       </c>
@@ -4645,10 +4652,10 @@
       <c r="D112" s="23"/>
       <c r="E112" s="23"/>
       <c r="F112" s="23"/>
-      <c r="G112" s="24"/>
+      <c r="G112" s="29"/>
       <c r="H112" s="23"/>
-      <c r="I112" s="28"/>
-      <c r="J112" s="25"/>
+      <c r="I112" s="27"/>
+      <c r="J112" s="28"/>
       <c r="L112" s="12" t="s">
         <v>15</v>
       </c>
@@ -4678,10 +4685,10 @@
       <c r="D113" s="23"/>
       <c r="E113" s="23"/>
       <c r="F113" s="23"/>
-      <c r="G113" s="24"/>
+      <c r="G113" s="29"/>
       <c r="H113" s="23"/>
-      <c r="I113" s="28"/>
-      <c r="J113" s="25"/>
+      <c r="I113" s="27"/>
+      <c r="J113" s="28"/>
       <c r="L113" s="14" t="s">
         <v>17</v>
       </c>
@@ -4709,10 +4716,10 @@
       <c r="D114" s="23"/>
       <c r="E114" s="23"/>
       <c r="F114" s="23"/>
-      <c r="G114" s="24"/>
+      <c r="G114" s="29"/>
       <c r="H114" s="23"/>
-      <c r="I114" s="28"/>
-      <c r="J114" s="25"/>
+      <c r="I114" s="27"/>
+      <c r="J114" s="28"/>
       <c r="L114" s="15" t="s">
         <v>23</v>
       </c>
@@ -4739,19 +4746,19 @@
       </c>
       <c r="D115" s="23"/>
       <c r="E115" s="23"/>
-      <c r="F115" s="28" t="s">
+      <c r="F115" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G115" s="28" t="s">
+      <c r="G115" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H115" s="28" t="s">
+      <c r="H115" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I115" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J115" s="29" t="s">
+      <c r="I115" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J115" s="24" t="s">
         <v>34</v>
       </c>
       <c r="L115" s="9" t="s">
@@ -4782,11 +4789,11 @@
       <c r="C116" s="23"/>
       <c r="D116" s="23"/>
       <c r="E116" s="23"/>
-      <c r="F116" s="28"/>
-      <c r="G116" s="28"/>
-      <c r="H116" s="28"/>
-      <c r="I116" s="25"/>
-      <c r="J116" s="29"/>
+      <c r="F116" s="27"/>
+      <c r="G116" s="27"/>
+      <c r="H116" s="27"/>
+      <c r="I116" s="28"/>
+      <c r="J116" s="24"/>
       <c r="L116" s="11" t="s">
         <v>5</v>
       </c>
@@ -4825,11 +4832,11 @@
       <c r="C117" s="23"/>
       <c r="D117" s="23"/>
       <c r="E117" s="23"/>
-      <c r="F117" s="28"/>
-      <c r="G117" s="28"/>
-      <c r="H117" s="28"/>
-      <c r="I117" s="25"/>
-      <c r="J117" s="29"/>
+      <c r="F117" s="27"/>
+      <c r="G117" s="27"/>
+      <c r="H117" s="27"/>
+      <c r="I117" s="28"/>
+      <c r="J117" s="24"/>
       <c r="L117" s="12" t="s">
         <v>15</v>
       </c>
@@ -4858,11 +4865,11 @@
       <c r="C118" s="23"/>
       <c r="D118" s="23"/>
       <c r="E118" s="23"/>
-      <c r="F118" s="28"/>
-      <c r="G118" s="28"/>
-      <c r="H118" s="28"/>
-      <c r="I118" s="25"/>
-      <c r="J118" s="29"/>
+      <c r="F118" s="27"/>
+      <c r="G118" s="27"/>
+      <c r="H118" s="27"/>
+      <c r="I118" s="28"/>
+      <c r="J118" s="24"/>
       <c r="L118" s="14" t="s">
         <v>17</v>
       </c>
@@ -4889,11 +4896,11 @@
       <c r="C119" s="23"/>
       <c r="D119" s="23"/>
       <c r="E119" s="23"/>
-      <c r="F119" s="28"/>
-      <c r="G119" s="28"/>
-      <c r="H119" s="28"/>
-      <c r="I119" s="25"/>
-      <c r="J119" s="29"/>
+      <c r="F119" s="27"/>
+      <c r="G119" s="27"/>
+      <c r="H119" s="27"/>
+      <c r="I119" s="28"/>
+      <c r="J119" s="24"/>
       <c r="L119" s="15" t="s">
         <v>23</v>
       </c>
@@ -4933,10 +4940,10 @@
       <c r="G122" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H122" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I122" s="26" t="s">
+      <c r="H122" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I122" s="25" t="s">
         <v>41</v>
       </c>
       <c r="J122" s="23"/>
@@ -4970,8 +4977,8 @@
       <c r="E123" s="23"/>
       <c r="F123" s="23"/>
       <c r="G123" s="23"/>
-      <c r="H123" s="24"/>
-      <c r="I123" s="27"/>
+      <c r="H123" s="29"/>
+      <c r="I123" s="26"/>
       <c r="J123" s="23"/>
       <c r="L123" s="11" t="s">
         <v>5</v>
@@ -5013,8 +5020,8 @@
       <c r="E124" s="23"/>
       <c r="F124" s="23"/>
       <c r="G124" s="23"/>
-      <c r="H124" s="24"/>
-      <c r="I124" s="27"/>
+      <c r="H124" s="29"/>
+      <c r="I124" s="26"/>
       <c r="J124" s="23"/>
       <c r="L124" s="12" t="s">
         <v>15</v>
@@ -5038,8 +5045,8 @@
       <c r="E125" s="23"/>
       <c r="F125" s="23"/>
       <c r="G125" s="23"/>
-      <c r="H125" s="24"/>
-      <c r="I125" s="27"/>
+      <c r="H125" s="29"/>
+      <c r="I125" s="26"/>
       <c r="J125" s="23"/>
       <c r="L125" s="14" t="s">
         <v>17</v>
@@ -5069,8 +5076,8 @@
       <c r="E126" s="23"/>
       <c r="F126" s="23"/>
       <c r="G126" s="23"/>
-      <c r="H126" s="24"/>
-      <c r="I126" s="27"/>
+      <c r="H126" s="29"/>
+      <c r="I126" s="26"/>
       <c r="J126" s="23"/>
       <c r="L126" s="15" t="s">
         <v>23</v>
@@ -5098,7 +5105,7 @@
       </c>
       <c r="D127" s="23"/>
       <c r="E127" s="23"/>
-      <c r="F127" s="24" t="s">
+      <c r="F127" s="29" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="23" t="s">
@@ -5107,10 +5114,10 @@
       <c r="H127" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="I127" s="28" t="s">
+      <c r="I127" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J127" s="25" t="s">
+      <c r="J127" s="28" t="s">
         <v>26</v>
       </c>
       <c r="L127" s="9" t="s">
@@ -5141,11 +5148,11 @@
       <c r="C128" s="23"/>
       <c r="D128" s="23"/>
       <c r="E128" s="23"/>
-      <c r="F128" s="24"/>
+      <c r="F128" s="29"/>
       <c r="G128" s="23"/>
       <c r="H128" s="23"/>
-      <c r="I128" s="28"/>
-      <c r="J128" s="25"/>
+      <c r="I128" s="27"/>
+      <c r="J128" s="28"/>
       <c r="L128" s="11" t="s">
         <v>5</v>
       </c>
@@ -5184,11 +5191,11 @@
       <c r="C129" s="23"/>
       <c r="D129" s="23"/>
       <c r="E129" s="23"/>
-      <c r="F129" s="24"/>
+      <c r="F129" s="29"/>
       <c r="G129" s="23"/>
       <c r="H129" s="23"/>
-      <c r="I129" s="28"/>
-      <c r="J129" s="25"/>
+      <c r="I129" s="27"/>
+      <c r="J129" s="28"/>
       <c r="L129" s="12" t="s">
         <v>15</v>
       </c>
@@ -5217,11 +5224,11 @@
       <c r="C130" s="23"/>
       <c r="D130" s="23"/>
       <c r="E130" s="23"/>
-      <c r="F130" s="24"/>
+      <c r="F130" s="29"/>
       <c r="G130" s="23"/>
       <c r="H130" s="23"/>
-      <c r="I130" s="28"/>
-      <c r="J130" s="25"/>
+      <c r="I130" s="27"/>
+      <c r="J130" s="28"/>
       <c r="L130" s="14" t="s">
         <v>17</v>
       </c>
@@ -5248,11 +5255,11 @@
       <c r="C131" s="23"/>
       <c r="D131" s="23"/>
       <c r="E131" s="23"/>
-      <c r="F131" s="24"/>
+      <c r="F131" s="29"/>
       <c r="G131" s="23"/>
       <c r="H131" s="23"/>
-      <c r="I131" s="28"/>
-      <c r="J131" s="25"/>
+      <c r="I131" s="27"/>
+      <c r="J131" s="28"/>
       <c r="L131" s="15" t="s">
         <v>23</v>
       </c>
@@ -5279,19 +5286,19 @@
       </c>
       <c r="D132" s="23"/>
       <c r="E132" s="23"/>
-      <c r="F132" s="28" t="s">
+      <c r="F132" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G132" s="28" t="s">
+      <c r="G132" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H132" s="28" t="s">
+      <c r="H132" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I132" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J132" s="29" t="s">
+      <c r="I132" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J132" s="24" t="s">
         <v>34</v>
       </c>
       <c r="L132" s="9" t="s">
@@ -5322,11 +5329,11 @@
       <c r="C133" s="23"/>
       <c r="D133" s="23"/>
       <c r="E133" s="23"/>
-      <c r="F133" s="28"/>
-      <c r="G133" s="28"/>
-      <c r="H133" s="28"/>
-      <c r="I133" s="25"/>
-      <c r="J133" s="29"/>
+      <c r="F133" s="27"/>
+      <c r="G133" s="27"/>
+      <c r="H133" s="27"/>
+      <c r="I133" s="28"/>
+      <c r="J133" s="24"/>
       <c r="L133" s="11" t="s">
         <v>5</v>
       </c>
@@ -5365,11 +5372,11 @@
       <c r="C134" s="23"/>
       <c r="D134" s="23"/>
       <c r="E134" s="23"/>
-      <c r="F134" s="28"/>
-      <c r="G134" s="28"/>
-      <c r="H134" s="28"/>
-      <c r="I134" s="25"/>
-      <c r="J134" s="29"/>
+      <c r="F134" s="27"/>
+      <c r="G134" s="27"/>
+      <c r="H134" s="27"/>
+      <c r="I134" s="28"/>
+      <c r="J134" s="24"/>
       <c r="L134" s="12" t="s">
         <v>15</v>
       </c>
@@ -5398,11 +5405,11 @@
       <c r="C135" s="23"/>
       <c r="D135" s="23"/>
       <c r="E135" s="23"/>
-      <c r="F135" s="28"/>
-      <c r="G135" s="28"/>
-      <c r="H135" s="28"/>
-      <c r="I135" s="25"/>
-      <c r="J135" s="29"/>
+      <c r="F135" s="27"/>
+      <c r="G135" s="27"/>
+      <c r="H135" s="27"/>
+      <c r="I135" s="28"/>
+      <c r="J135" s="24"/>
       <c r="L135" s="14" t="s">
         <v>17</v>
       </c>
@@ -5429,11 +5436,11 @@
       <c r="C136" s="23"/>
       <c r="D136" s="23"/>
       <c r="E136" s="23"/>
-      <c r="F136" s="28"/>
-      <c r="G136" s="28"/>
-      <c r="H136" s="28"/>
-      <c r="I136" s="25"/>
-      <c r="J136" s="29"/>
+      <c r="F136" s="27"/>
+      <c r="G136" s="27"/>
+      <c r="H136" s="27"/>
+      <c r="I136" s="28"/>
+      <c r="J136" s="24"/>
       <c r="L136" s="15" t="s">
         <v>23</v>
       </c>
@@ -5469,7 +5476,7 @@
       <c r="F140" s="23"/>
       <c r="G140" s="23"/>
       <c r="H140" s="23"/>
-      <c r="I140" s="26" t="s">
+      <c r="I140" s="25" t="s">
         <v>41</v>
       </c>
       <c r="J140" s="23"/>
@@ -5501,7 +5508,7 @@
       <c r="F141" s="23"/>
       <c r="G141" s="23"/>
       <c r="H141" s="23"/>
-      <c r="I141" s="27"/>
+      <c r="I141" s="26"/>
       <c r="J141" s="23"/>
       <c r="L141" s="11" t="s">
         <v>5</v>
@@ -5544,7 +5551,7 @@
       <c r="F142" s="23"/>
       <c r="G142" s="23"/>
       <c r="H142" s="23"/>
-      <c r="I142" s="27"/>
+      <c r="I142" s="26"/>
       <c r="J142" s="23"/>
       <c r="L142" s="12" t="s">
         <v>15</v>
@@ -5569,7 +5576,7 @@
       <c r="F143" s="23"/>
       <c r="G143" s="23"/>
       <c r="H143" s="23"/>
-      <c r="I143" s="27"/>
+      <c r="I143" s="26"/>
       <c r="J143" s="23"/>
       <c r="L143" s="14" t="s">
         <v>17</v>
@@ -5599,7 +5606,7 @@
       <c r="F144" s="23"/>
       <c r="G144" s="23"/>
       <c r="H144" s="23"/>
-      <c r="I144" s="27"/>
+      <c r="I144" s="26"/>
       <c r="J144" s="23"/>
       <c r="L144" s="15" t="s">
         <v>23</v>
@@ -5625,10 +5632,10 @@
       <c r="F145" s="23"/>
       <c r="G145" s="23"/>
       <c r="H145" s="23"/>
-      <c r="I145" s="28" t="s">
+      <c r="I145" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J145" s="25" t="s">
+      <c r="J145" s="28" t="s">
         <v>26</v>
       </c>
       <c r="L145" s="9" t="s">
@@ -5659,8 +5666,8 @@
       <c r="F146" s="23"/>
       <c r="G146" s="23"/>
       <c r="H146" s="23"/>
-      <c r="I146" s="28"/>
-      <c r="J146" s="25"/>
+      <c r="I146" s="27"/>
+      <c r="J146" s="28"/>
       <c r="L146" s="11" t="s">
         <v>5</v>
       </c>
@@ -5702,8 +5709,8 @@
       <c r="F147" s="23"/>
       <c r="G147" s="23"/>
       <c r="H147" s="23"/>
-      <c r="I147" s="28"/>
-      <c r="J147" s="25"/>
+      <c r="I147" s="27"/>
+      <c r="J147" s="28"/>
       <c r="L147" s="12" t="s">
         <v>15</v>
       </c>
@@ -5735,8 +5742,8 @@
       <c r="F148" s="23"/>
       <c r="G148" s="23"/>
       <c r="H148" s="23"/>
-      <c r="I148" s="28"/>
-      <c r="J148" s="25"/>
+      <c r="I148" s="27"/>
+      <c r="J148" s="28"/>
       <c r="L148" s="14" t="s">
         <v>17</v>
       </c>
@@ -5765,8 +5772,8 @@
       <c r="F149" s="23"/>
       <c r="G149" s="23"/>
       <c r="H149" s="23"/>
-      <c r="I149" s="28"/>
-      <c r="J149" s="25"/>
+      <c r="I149" s="27"/>
+      <c r="J149" s="28"/>
       <c r="L149" s="15" t="s">
         <v>23</v>
       </c>
@@ -5795,7 +5802,7 @@
       <c r="G150" s="23"/>
       <c r="H150" s="23"/>
       <c r="I150" s="23"/>
-      <c r="J150" s="29" t="s">
+      <c r="J150" s="24" t="s">
         <v>34</v>
       </c>
       <c r="L150" s="9" t="s">
@@ -5830,7 +5837,7 @@
       <c r="G151" s="23"/>
       <c r="H151" s="23"/>
       <c r="I151" s="23"/>
-      <c r="J151" s="29"/>
+      <c r="J151" s="24"/>
       <c r="L151" s="11" t="s">
         <v>5</v>
       </c>
@@ -5873,7 +5880,7 @@
       <c r="G152" s="23"/>
       <c r="H152" s="23"/>
       <c r="I152" s="23"/>
-      <c r="J152" s="29"/>
+      <c r="J152" s="24"/>
       <c r="L152" s="12" t="s">
         <v>15</v>
       </c>
@@ -5898,7 +5905,7 @@
       <c r="G153" s="23"/>
       <c r="H153" s="23"/>
       <c r="I153" s="23"/>
-      <c r="J153" s="29"/>
+      <c r="J153" s="24"/>
       <c r="L153" s="14" t="s">
         <v>17</v>
       </c>
@@ -5929,7 +5936,7 @@
       <c r="G154" s="23"/>
       <c r="H154" s="23"/>
       <c r="I154" s="23"/>
-      <c r="J154" s="29"/>
+      <c r="J154" s="24"/>
       <c r="L154" s="15" t="s">
         <v>23</v>
       </c>
@@ -5949,6 +5956,198 @@
     </row>
   </sheetData>
   <mergeCells count="216">
+    <mergeCell ref="I7:I11"/>
+    <mergeCell ref="J7:J11"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="G12:G16"/>
+    <mergeCell ref="H12:H16"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="J12:J16"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="H7:H11"/>
+    <mergeCell ref="I17:I21"/>
+    <mergeCell ref="J17:J21"/>
+    <mergeCell ref="C24:C28"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="F24:F28"/>
+    <mergeCell ref="G24:G28"/>
+    <mergeCell ref="H24:H28"/>
+    <mergeCell ref="I24:I28"/>
+    <mergeCell ref="J24:J28"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="E17:E21"/>
+    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="G17:G21"/>
+    <mergeCell ref="H17:H21"/>
+    <mergeCell ref="I29:I33"/>
+    <mergeCell ref="J29:J33"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="E34:E38"/>
+    <mergeCell ref="F34:F38"/>
+    <mergeCell ref="G34:G38"/>
+    <mergeCell ref="H34:H38"/>
+    <mergeCell ref="I34:I38"/>
+    <mergeCell ref="J34:J38"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="D29:D33"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="H29:H33"/>
+    <mergeCell ref="I40:I44"/>
+    <mergeCell ref="J40:J44"/>
+    <mergeCell ref="C45:C49"/>
+    <mergeCell ref="D45:D49"/>
+    <mergeCell ref="E45:E49"/>
+    <mergeCell ref="F45:F49"/>
+    <mergeCell ref="G45:G49"/>
+    <mergeCell ref="H45:H49"/>
+    <mergeCell ref="I45:I49"/>
+    <mergeCell ref="J45:J49"/>
+    <mergeCell ref="C40:C44"/>
+    <mergeCell ref="D40:D44"/>
+    <mergeCell ref="E40:E44"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="H40:H44"/>
+    <mergeCell ref="I50:I54"/>
+    <mergeCell ref="J50:J54"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="D56:D60"/>
+    <mergeCell ref="E56:E60"/>
+    <mergeCell ref="F56:F60"/>
+    <mergeCell ref="G56:G60"/>
+    <mergeCell ref="H56:H60"/>
+    <mergeCell ref="I56:I60"/>
+    <mergeCell ref="J56:J60"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="D50:D54"/>
+    <mergeCell ref="E50:E54"/>
+    <mergeCell ref="F50:F54"/>
+    <mergeCell ref="G50:G54"/>
+    <mergeCell ref="H50:H54"/>
+    <mergeCell ref="I61:I65"/>
+    <mergeCell ref="J61:J65"/>
+    <mergeCell ref="C66:C70"/>
+    <mergeCell ref="D66:D70"/>
+    <mergeCell ref="E66:E70"/>
+    <mergeCell ref="F66:F70"/>
+    <mergeCell ref="G66:G70"/>
+    <mergeCell ref="H66:H70"/>
+    <mergeCell ref="I66:I70"/>
+    <mergeCell ref="J66:J70"/>
+    <mergeCell ref="C61:C65"/>
+    <mergeCell ref="D61:D65"/>
+    <mergeCell ref="E61:E65"/>
+    <mergeCell ref="F61:F65"/>
+    <mergeCell ref="G61:G65"/>
+    <mergeCell ref="H61:H65"/>
+    <mergeCell ref="I73:I77"/>
+    <mergeCell ref="J73:J77"/>
+    <mergeCell ref="C78:C82"/>
+    <mergeCell ref="D78:D82"/>
+    <mergeCell ref="E78:E82"/>
+    <mergeCell ref="F78:F82"/>
+    <mergeCell ref="G78:G82"/>
+    <mergeCell ref="H78:H82"/>
+    <mergeCell ref="I78:I82"/>
+    <mergeCell ref="J78:J82"/>
+    <mergeCell ref="C73:C77"/>
+    <mergeCell ref="D73:D77"/>
+    <mergeCell ref="E73:E77"/>
+    <mergeCell ref="F73:F77"/>
+    <mergeCell ref="G73:G77"/>
+    <mergeCell ref="H73:H77"/>
+    <mergeCell ref="I83:I87"/>
+    <mergeCell ref="J83:J87"/>
+    <mergeCell ref="C89:C93"/>
+    <mergeCell ref="D89:D93"/>
+    <mergeCell ref="E89:E93"/>
+    <mergeCell ref="F89:F93"/>
+    <mergeCell ref="G89:G93"/>
+    <mergeCell ref="H89:H93"/>
+    <mergeCell ref="I89:I93"/>
+    <mergeCell ref="J89:J93"/>
+    <mergeCell ref="C83:C87"/>
+    <mergeCell ref="D83:D87"/>
+    <mergeCell ref="E83:E87"/>
+    <mergeCell ref="F83:F87"/>
+    <mergeCell ref="G83:G87"/>
+    <mergeCell ref="H83:H87"/>
+    <mergeCell ref="I94:I98"/>
+    <mergeCell ref="J94:J98"/>
+    <mergeCell ref="C99:C103"/>
+    <mergeCell ref="D99:D103"/>
+    <mergeCell ref="E99:E103"/>
+    <mergeCell ref="F99:F103"/>
+    <mergeCell ref="G99:G103"/>
+    <mergeCell ref="H99:H103"/>
+    <mergeCell ref="I99:I103"/>
+    <mergeCell ref="J99:J103"/>
+    <mergeCell ref="C94:C98"/>
+    <mergeCell ref="D94:D98"/>
+    <mergeCell ref="E94:E98"/>
+    <mergeCell ref="F94:F98"/>
+    <mergeCell ref="G94:G98"/>
+    <mergeCell ref="H94:H98"/>
+    <mergeCell ref="I105:I109"/>
+    <mergeCell ref="J105:J109"/>
+    <mergeCell ref="C110:C114"/>
+    <mergeCell ref="D110:D114"/>
+    <mergeCell ref="E110:E114"/>
+    <mergeCell ref="F110:F114"/>
+    <mergeCell ref="G110:G114"/>
+    <mergeCell ref="H110:H114"/>
+    <mergeCell ref="I110:I114"/>
+    <mergeCell ref="J110:J114"/>
+    <mergeCell ref="C105:C109"/>
+    <mergeCell ref="D105:D109"/>
+    <mergeCell ref="E105:E109"/>
+    <mergeCell ref="F105:F109"/>
+    <mergeCell ref="G105:G109"/>
+    <mergeCell ref="H105:H109"/>
+    <mergeCell ref="I115:I119"/>
+    <mergeCell ref="J115:J119"/>
+    <mergeCell ref="C122:C126"/>
+    <mergeCell ref="D122:D126"/>
+    <mergeCell ref="E122:E126"/>
+    <mergeCell ref="F122:F126"/>
+    <mergeCell ref="G122:G126"/>
+    <mergeCell ref="H122:H126"/>
+    <mergeCell ref="I122:I126"/>
+    <mergeCell ref="J122:J126"/>
+    <mergeCell ref="C115:C119"/>
+    <mergeCell ref="D115:D119"/>
+    <mergeCell ref="E115:E119"/>
+    <mergeCell ref="F115:F119"/>
+    <mergeCell ref="G115:G119"/>
+    <mergeCell ref="H115:H119"/>
+    <mergeCell ref="I127:I131"/>
+    <mergeCell ref="J127:J131"/>
+    <mergeCell ref="C132:C136"/>
+    <mergeCell ref="D132:D136"/>
+    <mergeCell ref="E132:E136"/>
+    <mergeCell ref="F132:F136"/>
+    <mergeCell ref="G132:G136"/>
+    <mergeCell ref="H132:H136"/>
+    <mergeCell ref="I132:I136"/>
+    <mergeCell ref="J132:J136"/>
+    <mergeCell ref="C127:C131"/>
+    <mergeCell ref="D127:D131"/>
+    <mergeCell ref="E127:E131"/>
+    <mergeCell ref="F127:F131"/>
+    <mergeCell ref="G127:G131"/>
+    <mergeCell ref="H127:H131"/>
     <mergeCell ref="I150:I154"/>
     <mergeCell ref="J150:J154"/>
     <mergeCell ref="C150:C154"/>
@@ -5973,198 +6172,6 @@
     <mergeCell ref="F140:F144"/>
     <mergeCell ref="G140:G144"/>
     <mergeCell ref="H140:H144"/>
-    <mergeCell ref="I127:I131"/>
-    <mergeCell ref="J127:J131"/>
-    <mergeCell ref="C132:C136"/>
-    <mergeCell ref="D132:D136"/>
-    <mergeCell ref="E132:E136"/>
-    <mergeCell ref="F132:F136"/>
-    <mergeCell ref="G132:G136"/>
-    <mergeCell ref="H132:H136"/>
-    <mergeCell ref="I132:I136"/>
-    <mergeCell ref="J132:J136"/>
-    <mergeCell ref="C127:C131"/>
-    <mergeCell ref="D127:D131"/>
-    <mergeCell ref="E127:E131"/>
-    <mergeCell ref="F127:F131"/>
-    <mergeCell ref="G127:G131"/>
-    <mergeCell ref="H127:H131"/>
-    <mergeCell ref="I115:I119"/>
-    <mergeCell ref="J115:J119"/>
-    <mergeCell ref="C122:C126"/>
-    <mergeCell ref="D122:D126"/>
-    <mergeCell ref="E122:E126"/>
-    <mergeCell ref="F122:F126"/>
-    <mergeCell ref="G122:G126"/>
-    <mergeCell ref="H122:H126"/>
-    <mergeCell ref="I122:I126"/>
-    <mergeCell ref="J122:J126"/>
-    <mergeCell ref="C115:C119"/>
-    <mergeCell ref="D115:D119"/>
-    <mergeCell ref="E115:E119"/>
-    <mergeCell ref="F115:F119"/>
-    <mergeCell ref="G115:G119"/>
-    <mergeCell ref="H115:H119"/>
-    <mergeCell ref="I105:I109"/>
-    <mergeCell ref="J105:J109"/>
-    <mergeCell ref="C110:C114"/>
-    <mergeCell ref="D110:D114"/>
-    <mergeCell ref="E110:E114"/>
-    <mergeCell ref="F110:F114"/>
-    <mergeCell ref="G110:G114"/>
-    <mergeCell ref="H110:H114"/>
-    <mergeCell ref="I110:I114"/>
-    <mergeCell ref="J110:J114"/>
-    <mergeCell ref="C105:C109"/>
-    <mergeCell ref="D105:D109"/>
-    <mergeCell ref="E105:E109"/>
-    <mergeCell ref="F105:F109"/>
-    <mergeCell ref="G105:G109"/>
-    <mergeCell ref="H105:H109"/>
-    <mergeCell ref="I94:I98"/>
-    <mergeCell ref="J94:J98"/>
-    <mergeCell ref="C99:C103"/>
-    <mergeCell ref="D99:D103"/>
-    <mergeCell ref="E99:E103"/>
-    <mergeCell ref="F99:F103"/>
-    <mergeCell ref="G99:G103"/>
-    <mergeCell ref="H99:H103"/>
-    <mergeCell ref="I99:I103"/>
-    <mergeCell ref="J99:J103"/>
-    <mergeCell ref="C94:C98"/>
-    <mergeCell ref="D94:D98"/>
-    <mergeCell ref="E94:E98"/>
-    <mergeCell ref="F94:F98"/>
-    <mergeCell ref="G94:G98"/>
-    <mergeCell ref="H94:H98"/>
-    <mergeCell ref="I83:I87"/>
-    <mergeCell ref="J83:J87"/>
-    <mergeCell ref="C89:C93"/>
-    <mergeCell ref="D89:D93"/>
-    <mergeCell ref="E89:E93"/>
-    <mergeCell ref="F89:F93"/>
-    <mergeCell ref="G89:G93"/>
-    <mergeCell ref="H89:H93"/>
-    <mergeCell ref="I89:I93"/>
-    <mergeCell ref="J89:J93"/>
-    <mergeCell ref="C83:C87"/>
-    <mergeCell ref="D83:D87"/>
-    <mergeCell ref="E83:E87"/>
-    <mergeCell ref="F83:F87"/>
-    <mergeCell ref="G83:G87"/>
-    <mergeCell ref="H83:H87"/>
-    <mergeCell ref="I73:I77"/>
-    <mergeCell ref="J73:J77"/>
-    <mergeCell ref="C78:C82"/>
-    <mergeCell ref="D78:D82"/>
-    <mergeCell ref="E78:E82"/>
-    <mergeCell ref="F78:F82"/>
-    <mergeCell ref="G78:G82"/>
-    <mergeCell ref="H78:H82"/>
-    <mergeCell ref="I78:I82"/>
-    <mergeCell ref="J78:J82"/>
-    <mergeCell ref="C73:C77"/>
-    <mergeCell ref="D73:D77"/>
-    <mergeCell ref="E73:E77"/>
-    <mergeCell ref="F73:F77"/>
-    <mergeCell ref="G73:G77"/>
-    <mergeCell ref="H73:H77"/>
-    <mergeCell ref="I61:I65"/>
-    <mergeCell ref="J61:J65"/>
-    <mergeCell ref="C66:C70"/>
-    <mergeCell ref="D66:D70"/>
-    <mergeCell ref="E66:E70"/>
-    <mergeCell ref="F66:F70"/>
-    <mergeCell ref="G66:G70"/>
-    <mergeCell ref="H66:H70"/>
-    <mergeCell ref="I66:I70"/>
-    <mergeCell ref="J66:J70"/>
-    <mergeCell ref="C61:C65"/>
-    <mergeCell ref="D61:D65"/>
-    <mergeCell ref="E61:E65"/>
-    <mergeCell ref="F61:F65"/>
-    <mergeCell ref="G61:G65"/>
-    <mergeCell ref="H61:H65"/>
-    <mergeCell ref="I50:I54"/>
-    <mergeCell ref="J50:J54"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="D56:D60"/>
-    <mergeCell ref="E56:E60"/>
-    <mergeCell ref="F56:F60"/>
-    <mergeCell ref="G56:G60"/>
-    <mergeCell ref="H56:H60"/>
-    <mergeCell ref="I56:I60"/>
-    <mergeCell ref="J56:J60"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="D50:D54"/>
-    <mergeCell ref="E50:E54"/>
-    <mergeCell ref="F50:F54"/>
-    <mergeCell ref="G50:G54"/>
-    <mergeCell ref="H50:H54"/>
-    <mergeCell ref="I40:I44"/>
-    <mergeCell ref="J40:J44"/>
-    <mergeCell ref="C45:C49"/>
-    <mergeCell ref="D45:D49"/>
-    <mergeCell ref="E45:E49"/>
-    <mergeCell ref="F45:F49"/>
-    <mergeCell ref="G45:G49"/>
-    <mergeCell ref="H45:H49"/>
-    <mergeCell ref="I45:I49"/>
-    <mergeCell ref="J45:J49"/>
-    <mergeCell ref="C40:C44"/>
-    <mergeCell ref="D40:D44"/>
-    <mergeCell ref="E40:E44"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="G40:G44"/>
-    <mergeCell ref="H40:H44"/>
-    <mergeCell ref="I29:I33"/>
-    <mergeCell ref="J29:J33"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="E34:E38"/>
-    <mergeCell ref="F34:F38"/>
-    <mergeCell ref="G34:G38"/>
-    <mergeCell ref="H34:H38"/>
-    <mergeCell ref="I34:I38"/>
-    <mergeCell ref="J34:J38"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="D29:D33"/>
-    <mergeCell ref="E29:E33"/>
-    <mergeCell ref="F29:F33"/>
-    <mergeCell ref="G29:G33"/>
-    <mergeCell ref="H29:H33"/>
-    <mergeCell ref="I17:I21"/>
-    <mergeCell ref="J17:J21"/>
-    <mergeCell ref="C24:C28"/>
-    <mergeCell ref="D24:D28"/>
-    <mergeCell ref="E24:E28"/>
-    <mergeCell ref="F24:F28"/>
-    <mergeCell ref="G24:G28"/>
-    <mergeCell ref="H24:H28"/>
-    <mergeCell ref="I24:I28"/>
-    <mergeCell ref="J24:J28"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="E17:E21"/>
-    <mergeCell ref="F17:F21"/>
-    <mergeCell ref="G17:G21"/>
-    <mergeCell ref="H17:H21"/>
-    <mergeCell ref="I7:I11"/>
-    <mergeCell ref="J7:J11"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="G12:G16"/>
-    <mergeCell ref="H12:H16"/>
-    <mergeCell ref="I12:I16"/>
-    <mergeCell ref="J12:J16"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="F7:F11"/>
-    <mergeCell ref="G7:G11"/>
-    <mergeCell ref="H7:H11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
